--- a/05_Figures/F06_prediction/proteins/training/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_mcsa/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="166">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -131,49 +131,82 @@
     <t xml:space="preserve">COPS8</t>
   </si>
   <si>
+    <t xml:space="preserve">CUL5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NANS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB6A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS4X</t>
+  </si>
+  <si>
     <t xml:space="preserve">ADIRF</t>
   </si>
   <si>
-    <t xml:space="preserve">CUL5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NANS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB6A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS4X</t>
-  </si>
-  <si>
     <t xml:space="preserve">FAM114A2</t>
   </si>
   <si>
     <t xml:space="preserve">PDCD6</t>
   </si>
   <si>
+    <t xml:space="preserve">CALM1</t>
+  </si>
+  <si>
     <t xml:space="preserve">COPA</t>
   </si>
   <si>
+    <t xml:space="preserve">GNAS</t>
+  </si>
+  <si>
     <t xml:space="preserve">GPAT3</t>
   </si>
   <si>
+    <t xml:space="preserve">PPCS</t>
+  </si>
+  <si>
     <t xml:space="preserve">PUDP</t>
   </si>
   <si>
-    <t xml:space="preserve">CALM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPCS</t>
-  </si>
-  <si>
     <t xml:space="preserve">ADK</t>
   </si>
   <si>
     <t xml:space="preserve">CD9</t>
   </si>
   <si>
-    <t xml:space="preserve">GNAS</t>
+    <t xml:space="preserve">FBLN5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HLA-DRB5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LPP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSMD10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RAB1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCCPDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESYT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KPNA1</t>
   </si>
   <si>
     <t xml:space="preserve">MXRA7</t>
@@ -182,351 +215,285 @@
     <t xml:space="preserve">PCCB</t>
   </si>
   <si>
-    <t xml:space="preserve">PSMD10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCCPDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2G</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ESYT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FBLN5</t>
+    <t xml:space="preserve">PNPT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PYGM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPSA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBCB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FARSB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GMPPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSP90AA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RTRAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TPPP3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRMT10C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RACK1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COQ10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FHL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LZIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFV3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIPSNAP3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VDAC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADSL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AQP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARL6IP5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP5F1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CLYBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTPS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CYC1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDAH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDX39B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EHD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FDXR</t>
   </si>
   <si>
     <t xml:space="preserve">FSCN1</t>
   </si>
   <si>
-    <t xml:space="preserve">GMPPB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KPNA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LPP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PNPT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PYGM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPSA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TBCB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FARSB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSP90AA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RTRAF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COQ10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TPPP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RACK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRB5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OLA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS9</t>
+    <t xml:space="preserve">FUBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FXR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FYCO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GAA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GATD3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GNB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSTM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HNRNPU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JPT2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LANCL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LMAN2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LRPAP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPK12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAPRE2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCCC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MCTS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRPL49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MT-CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYO18A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFAF5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NT5C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4HB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PACSIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGLS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSME2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RASA4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL10A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPS8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S100A16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEPTIN9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPTBN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNCRIP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TFRC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TGM2</t>
   </si>
   <si>
     <t xml:space="preserve">TMLHE</t>
   </si>
   <si>
-    <t xml:space="preserve">TST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AQP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COPB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FHL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HSPH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFV3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4HB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PIN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRMT10C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VDAC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ADSL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDOC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARL6IP5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP5F1B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C6orf136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP4B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CLYBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTPS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CYC1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCTN4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDAH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDX39B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EHD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FDXR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FXR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FYCO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GAA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GATD3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GNB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSTM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HNRNPU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JPT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LANCL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LCP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMAN2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LRPAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LZIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MACROD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPK12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAPRE2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCCC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MCTS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYO18A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NHLRC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NIPSNAP3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NT5C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OSTC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PACSIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGK1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGLS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPP3CB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKAA1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSME2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RASA4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL10A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPS8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEPTIN9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPTBN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSBP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNCRIP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TALDO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TFRC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TGM2</t>
-  </si>
-  <si>
     <t xml:space="preserve">TOM1L2</t>
   </si>
   <si>
     <t xml:space="preserve">TOMM40</t>
   </si>
   <si>
-    <t xml:space="preserve">TPI1</t>
-  </si>
-  <si>
     <t xml:space="preserve">TSFM</t>
   </si>
   <si>
@@ -543,9 +510,6 @@
   </si>
   <si>
     <t xml:space="preserve">VDAC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPS26A</t>
   </si>
   <si>
     <t xml:space="preserve">XRCC5</t>
@@ -935,16 +899,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.447373019139779</v>
+        <v>-0.41219621739049</v>
       </c>
       <c r="I2" t="n">
-        <v>0.138461538461538</v>
+        <v>0.0417582417582418</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -968,29 +932,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.447373019139779</v>
+        <v>-0.41219621739049</v>
       </c>
       <c r="I3" t="n">
-        <v>0.138461538461538</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.402985074626866</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.248756218905473</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.720158960711017</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.638187775019311</v>
-      </c>
+        <v>0.0417582417582418</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1014,2206 +970,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-1.18605644284675</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-0.239790257201899</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-1.24345062139813</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.66678253958495</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.744602035796467</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>-0.334400814647115</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.901554106865861</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-2.39705444624994</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>-0.728874607985399</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-0.635517245838556</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.579381681965325</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.965662089127403</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.63566682302662</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.0719558899243509</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>-0.358834783005562</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-0.759682221612871</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.079803905415755</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.434730838526445</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-0.29732732568763</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-0.477714192608337</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.11133857692648</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>0.066563020497131</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-0.441814311426966</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-1.66312403297041</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.321574506905559</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.70190232153644</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>-0.946619388316606</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.511341256438921</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.902514744550787</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.55831319193866</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.293191196453886</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-0.853769949628713</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-1.058041064589</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-1.49982017634822</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.49355891413014</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.399339374001674</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-0.0172139538617195</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>-0.45810111657076</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-1.32517216616723</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>-0.652303952102551</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-1.91111719078067</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-0.339987614820648</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-0.439410927446676</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-1.76109365544442</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.63749186875687</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.409973006769445</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.828453057055386</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.319959270560806</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-1.04561533348264</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.568776184499307</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.333370197400799</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>0.0211569171145655</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-1.51499019468451</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.367976330626165</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.31894961674766</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.767799827476757</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-1.04277205930557</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-0.256470872712634</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-0.633520406477209</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>-0.783353903221699</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.570573937254476</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.489453952944013</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-0.107753589969853</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-1.05507085192212</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>-0.283203637401733</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.107692127980755</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.10731980752868</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.350462778033403</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-0.250973722592608</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>0.067290658437968</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-0.468592269682986</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.81935510811425</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.966977929286864</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>0.0511294611271923</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.6150234780257</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.044033064799722</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.691100794001662</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-0.204402693454331</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-0.688183880723304</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.988474325207985</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-0.637949319046611</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>-0.0550982763096459</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>-0.917804451482637</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.08139411286293</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.406145439346332</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-1.12240859265256</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-0.245730002729369</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-1.23445060332851</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>0.171881395235042</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>0.10499445209969</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-1.31644430153721</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-1.52588596433372</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.08256852411847</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>-1.63690492737335</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-0.00354539350425931</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>-0.505202253346033</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.276327032448673</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.42054363219287</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-1.58026056046679</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>-0.357959860678309</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-1.08607134276406</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-0.462550175827673</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.21836426222657</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-2.03521932640367</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-1.14485737417791</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-0.307831208026035</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.358017259147358</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.307766452138563</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-1.03356560348134</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-1.34035328579791</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>-1.82255190937954</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.0867484290895144</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>-1.14636187181715</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>-0.100445714873266</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.03100800315764</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>-0.0620885442131347</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>0.139826099978891</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-0.364966684129319</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.23911098676343</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-1.26364132505815</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.633880254114296</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-0.126250575610096</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.449489283709391</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.758301410318643</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-2.36418803773043</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.690685296549262</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>-0.792829232068329</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-0.714945898267509</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.0664884469496205</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-0.399209533017304</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-2.99940738869464</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.0727741085784066</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>0.203767815251225</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-1.19539757207039</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.926494760585873</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.906930834185383</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-2.55234393721032</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.324052804426924</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>-0.401075196893979</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>-0.255133947768292</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.600498747368928</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>-0.978676620403296</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-0.21011179370558</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-0.789735463882103</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-2.20440378820871</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-1.17842050329765</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-2.73864380402071</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.258521565297446</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-1.42742497977685</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.256823140833792</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>0.247682021245115</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>0.0469170550595851</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>0.103897288632188</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-2.14226821683345</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-0.970421953968329</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.65261139236673</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.325424747458213</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-1.01475191856216</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>0.309155801991101</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-1.92298799681464</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-0.180915088935219</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-2.07603112988158</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.386816253625293</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.748519954234326</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.480741446263873</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-0.561421295715178</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>-0.634971787405305</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>-0.616454585649484</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.044896942585215</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>-0.438781637184714</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-0.168139324248178</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>0.273286456368509</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-1.27917544244144</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0.0992638512652272</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-1.7862586268005</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.076755583720691</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.453706736258399</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-1.5289492922118</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>-0.374676092107762</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.0833280902705718</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.504659328162543</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>-1.56864263414258</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-0.968468278513422</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>-1.01315232039236</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.868958850405149</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-0.752676110774293</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-1.2910002635175</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>-0.240605902095951</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>0.364005712512432</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-1.17072178686816</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-0.460681779728079</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-0.75304984576781</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.688266903439308</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-1.57910040362274</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.96923232176843</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.894652259067935</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.174124643803117</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-0.417715112544824</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-0.5155416209434</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-1.81986684377045</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3256,7 +1012,7 @@
         <v>1.706</v>
       </c>
       <c r="E2" t="n">
-        <v>2.23862974762449</v>
+        <v>1.74178393440636</v>
       </c>
     </row>
     <row r="3">
@@ -3273,7 +1029,7 @@
         <v>4.218</v>
       </c>
       <c r="E3" t="n">
-        <v>1.19119089241328</v>
+        <v>1.13645215380936</v>
       </c>
     </row>
     <row r="4">
@@ -3290,7 +1046,7 @@
         <v>1.578</v>
       </c>
       <c r="E4" t="n">
-        <v>0.662001042022595</v>
+        <v>0.710701929933722</v>
       </c>
     </row>
     <row r="5">
@@ -3307,7 +1063,7 @@
         <v>3.683</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5364169744155</v>
+        <v>2.18309544786349</v>
       </c>
     </row>
     <row r="6">
@@ -3324,7 +1080,7 @@
         <v>2.983</v>
       </c>
       <c r="E6" t="n">
-        <v>1.09359108585439</v>
+        <v>1.65761040512698</v>
       </c>
     </row>
     <row r="7">
@@ -3341,7 +1097,7 @@
         <v>2.44</v>
       </c>
       <c r="E7" t="n">
-        <v>3.10536418136749</v>
+        <v>2.98024986394367</v>
       </c>
     </row>
     <row r="8">
@@ -3358,7 +1114,7 @@
         <v>0.579999999999998</v>
       </c>
       <c r="E8" t="n">
-        <v>0.860789774745632</v>
+        <v>0.749422738293999</v>
       </c>
     </row>
     <row r="9">
@@ -3375,7 +1131,7 @@
         <v>-1.918</v>
       </c>
       <c r="E9" t="n">
-        <v>1.73897239100367</v>
+        <v>1.80734282394361</v>
       </c>
     </row>
     <row r="10">
@@ -3392,7 +1148,7 @@
         <v>0.672000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>0.579597429283657</v>
+        <v>0.595226186576404</v>
       </c>
     </row>
     <row r="11">
@@ -3409,7 +1165,7 @@
         <v>0.352999999999998</v>
       </c>
       <c r="E11" t="n">
-        <v>2.89164134498974</v>
+        <v>2.88359551981586</v>
       </c>
     </row>
     <row r="12">
@@ -3426,7 +1182,7 @@
         <v>5.08900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>0.87949554315558</v>
+        <v>0.747902017499187</v>
       </c>
     </row>
     <row r="13">
@@ -3443,7 +1199,7 @@
         <v>0.181000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.44947794640293</v>
+        <v>-1.95479443506155</v>
       </c>
     </row>
     <row r="14">
@@ -3460,7 +1216,7 @@
         <v>1.311</v>
       </c>
       <c r="E14" t="n">
-        <v>1.52891867041176</v>
+        <v>1.70329182707135</v>
       </c>
     </row>
     <row r="15">
@@ -3477,7 +1233,7 @@
         <v>2.862</v>
       </c>
       <c r="E15" t="n">
-        <v>0.734433983858596</v>
+        <v>0.686627473878662</v>
       </c>
     </row>
   </sheetData>
@@ -3553,10 +1309,10 @@
         <v>39</v>
       </c>
       <c r="D4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.928571428571429</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="5">
@@ -3570,10 +1326,10 @@
         <v>40</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="6">
@@ -3587,10 +1343,10 @@
         <v>41</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="7">
@@ -3604,10 +1360,10 @@
         <v>42</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.857142857142857</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="8">
@@ -3621,10 +1377,10 @@
         <v>43</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="9">
@@ -3638,10 +1394,10 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.785714285714286</v>
+        <v>0.714285714285714</v>
       </c>
     </row>
     <row r="10">
@@ -3655,10 +1411,10 @@
         <v>45</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="11">
@@ -3672,10 +1428,10 @@
         <v>46</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="12">
@@ -3689,10 +1445,10 @@
         <v>47</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="13">
@@ -3740,10 +1496,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
-        <v>0.571428571428571</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="16">
@@ -3757,10 +1513,10 @@
         <v>51</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="17">
@@ -3774,10 +1530,10 @@
         <v>52</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -3791,10 +1547,10 @@
         <v>53</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="19">
@@ -3808,10 +1564,10 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="20">
@@ -3825,10 +1581,10 @@
         <v>55</v>
       </c>
       <c r="D20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="21">
@@ -3842,10 +1598,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="22">
@@ -3859,10 +1615,10 @@
         <v>57</v>
       </c>
       <c r="D22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" t="n">
-        <v>0.571428571428571</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="23">
@@ -3910,10 +1666,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="26">
@@ -3927,10 +1683,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="27">
@@ -3944,10 +1700,10 @@
         <v>62</v>
       </c>
       <c r="D27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="28">
@@ -3961,10 +1717,10 @@
         <v>63</v>
       </c>
       <c r="D28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="29">
@@ -3978,10 +1734,10 @@
         <v>64</v>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="30">
@@ -3995,10 +1751,10 @@
         <v>65</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="31">
@@ -4012,10 +1768,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="32">
@@ -4029,10 +1785,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="33">
@@ -4046,10 +1802,10 @@
         <v>68</v>
       </c>
       <c r="D33" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="34">
@@ -4063,10 +1819,10 @@
         <v>69</v>
       </c>
       <c r="D34" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" t="n">
-        <v>0.5</v>
+        <v>0.428571428571429</v>
       </c>
     </row>
     <row r="35">
@@ -4097,10 +1853,10 @@
         <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="37">
@@ -4114,10 +1870,10 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="38">
@@ -4131,10 +1887,10 @@
         <v>73</v>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="39">
@@ -4148,10 +1904,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E39" t="n">
-        <v>0.428571428571429</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="40">
@@ -4233,10 +1989,10 @@
         <v>79</v>
       </c>
       <c r="D44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E44" t="n">
-        <v>0.214285714285714</v>
+        <v>0.285714285714286</v>
       </c>
     </row>
     <row r="45">
@@ -4318,10 +2074,10 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="50">
@@ -4471,10 +2227,10 @@
         <v>93</v>
       </c>
       <c r="D58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E58" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="59">
@@ -4488,10 +2244,10 @@
         <v>94</v>
       </c>
       <c r="D59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="60">
@@ -4505,10 +2261,10 @@
         <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="61">
@@ -4522,10 +2278,10 @@
         <v>96</v>
       </c>
       <c r="D61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E61" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="62">
@@ -4539,10 +2295,10 @@
         <v>97</v>
       </c>
       <c r="D62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="63">
@@ -5698,210 +3454,6 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="s">
-        <v>166</v>
-      </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
-      <c r="E131" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="s">
-        <v>167</v>
-      </c>
-      <c r="D132" t="n">
-        <v>1</v>
-      </c>
-      <c r="E132" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="s">
-        <v>168</v>
-      </c>
-      <c r="D133" t="n">
-        <v>1</v>
-      </c>
-      <c r="E133" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="s">
-        <v>169</v>
-      </c>
-      <c r="D134" t="n">
-        <v>1</v>
-      </c>
-      <c r="E134" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="s">
-        <v>170</v>
-      </c>
-      <c r="D135" t="n">
-        <v>1</v>
-      </c>
-      <c r="E135" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="s">
-        <v>171</v>
-      </c>
-      <c r="D136" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="s">
-        <v>172</v>
-      </c>
-      <c r="D137" t="n">
-        <v>1</v>
-      </c>
-      <c r="E137" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="s">
-        <v>173</v>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="s">
-        <v>174</v>
-      </c>
-      <c r="D139" t="n">
-        <v>1</v>
-      </c>
-      <c r="E139" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="s">
-        <v>175</v>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
-      </c>
-      <c r="E140" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="s">
-        <v>176</v>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
-      </c>
-      <c r="E141" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="s">
-        <v>177</v>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
-      </c>
-      <c r="E142" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/training/d_mcsa/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_mcsa/spls/c_data/results.xlsx
@@ -935,7 +935,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-0.41219621739049</v>
@@ -943,10 +943,18 @@
       <c r="I3" t="n">
         <v>0.0417582417582418</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.358208955223881</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.318407960199005</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.732620920781445</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.655233914847474</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -970,6 +978,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-1.29562064325375</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-0.272044959883933</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-1.08084069466823</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.632180826024902</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.727548745721305</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>-0.512234363789827</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.987820234144357</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-2.31624063877852</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.7187072034121</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.688332985184351</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.00060633851664</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-1.00982592426565</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.623493835128425</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.215201125912537</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>-0.534333374379535</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.657763650262314</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.343183420694759</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.316038413515918</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-0.215081428969134</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-0.419830357269086</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.12409649989609</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.0646558110254963</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-0.520682961064865</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-1.77471054239178</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.353996825815685</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.792776996657306</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>-0.710891076600425</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.545933368972499</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.824749670848212</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.4075803786039</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.221862269563953</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.901131863038329</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.769941966966452</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-1.16183293927527</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.349834376282359</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.608004911141271</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-0.148047022995751</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.438246460412354</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.976403908892592</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>-0.596129175108719</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-2.43950856149563</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-0.338507643879959</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-0.291290001456844</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-1.17760236099781</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-1.24269147694724</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.88605879170256</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.844058959113344</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.280688434749582</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-1.13089444623688</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.351741740564125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.427003560832898</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>0.0105479327575309</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-1.67021894966482</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.722485688657022</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-1.65222689041697</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-0.657557185724156</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-1.10416870703073</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-0.34850388712379</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-0.642699063687861</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.682876209584626</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-0.672933963314556</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.377974082184154</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-0.214857109208765</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-1.08561117411143</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>-0.121733072504196</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.109137411577074</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.301944062938134</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.707623866302507</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-0.165575085256608</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>0.31941736716131</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-0.559031567118517</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.9278540072355</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-0.994157141172263</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>0.00945173202279737</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.88407479534091</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>0.249970723814752</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.642420066863751</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-0.297850161681458</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-0.414856508866661</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.950090791807253</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-0.888162082455383</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>-0.0482207467135387</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>-0.901263474787576</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.08057015274709</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.502937706618755</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-0.97658089468301</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-0.243112346879604</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-1.1990666758525</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>0.0292294929231922</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>0.193957345543591</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-1.28960621118208</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.48105441338753</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.34782693349102</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>-1.68596139830235</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-0.0448062452687221</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>-0.573308052262684</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.153821649999311</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.375167833723987</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-2.64525359813704</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>-0.60209919894591</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-1.03449343860948</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-0.448767336699553</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.23547405551204</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-2.03016882380809</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.91643482776985</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.377005916231592</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.605185027243733</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.344056245031136</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-1.07529834202858</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-1.45880129459865</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-2.2347139426573</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.0847017493184146</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>-1.11466981459093</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>-0.180013045094916</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.24743529554245</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>-0.00379776974356205</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.144807879420245</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-0.248168533422219</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.27771438999849</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-1.05368393847303</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.732256355581942</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-0.161283578619274</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.475260583756545</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.698847972764018</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-2.1063455668278</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>-0.72549348084116</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>-0.841780298888531</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-0.706161079503405</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-0.0922289471101845</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-0.418006744166676</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-2.48614464820412</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.0551779836403077</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.252206149858008</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>-1.23613894546926</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.785080159843135</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.197311001511788</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-2.56024196573823</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.265129511291266</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>-0.363599963357535</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>-0.258433974046643</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.521606273516182</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>-0.933005814798288</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-0.272801696811252</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-0.808743449034428</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-2.23215925482707</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-1.14598876358139</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-2.37419166917119</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.360786661622339</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.96715556224239</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.14390237505113</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.135023252201919</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.295684471438378</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.196976681876995</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-2.31016773275581</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-1.30826166776079</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.575387455632825</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.249943470850573</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-1.08979564588025</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.298658462599865</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-2.03422283216692</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-0.197978237668104</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-2.06884080729623</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.432528087033368</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>-0.701075319696811</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.415113853054791</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-0.357203717606039</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>-0.704149807240772</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>-0.645921808458445</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.00231733272976231</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.420428780906592</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.0832866017977294</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.410914887422275</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>-1.47394384114421</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.0379961056175196</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-1.73894105330079</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.210080933437491</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.513652101126671</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-1.68034907502596</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>-0.324565056514291</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.10040530134387</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.474369301868627</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>-1.77212743241798</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-0.883170382894129</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.0166501644569974</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-1.3608960367007</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-0.703988965634168</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-1.46662199862661</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>-0.348085886163709</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.308556389120533</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-1.1691200138047</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-0.59459153467328</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.754824510749932</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.96746809720237</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-1.51058219067198</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.906349198166857</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-1.15057693616861</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.2631942818227</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-0.502937359932712</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.614574896771988</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-1.75453981135782</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
